--- a/data/trans_orig/P79A10_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79A10_2023-Clase-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15255</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11133</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19779</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>828</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>828</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20037</t>
+          <t>22263</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>25379</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39552</t>
+          <t>44260</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30414</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>50528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>51816</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41966</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59189</t>
+          <t>65365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21889</t>
+          <t>22412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25739</t>
+          <t>26541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52303</t>
+          <t>56794</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52303</t>
+          <t>56794</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52303</t>
+          <t>56794</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>73914</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>73914</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>73914</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23832</t>
+          <t>29212</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28117</t>
+          <t>35882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33075</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35839</t>
+          <t>42620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>56906</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49640</t>
+          <t>55874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62353</t>
+          <t>75889</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11590</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>32188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>41914</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>41914</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>41914</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>46148</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>46148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>46148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>88062</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>88062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>88062</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38476</t>
+          <t>43530</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>35315</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>49353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>45342</t>
+          <t>50185</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32440</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51758</t>
+          <t>55986</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24129</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25011</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>50586</t>
+          <t>55667</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50586</t>
+          <t>55667</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50586</t>
+          <t>55667</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>62322</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>62322</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>62322</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>109629</t>
+          <t>125830</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97733</t>
+          <t>109227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>136263</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>102671</t>
+          <t>119467</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87613</t>
+          <t>107637</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110151</t>
+          <t>127074</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>212300</t>
+          <t>245296</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>195537</t>
+          <t>226607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224113</t>
+          <t>258956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24544</t>
+          <t>29077</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36440</t>
+          <t>45680</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37463</t>
+          <t>36421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>46949</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>40008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63712</t>
+          <t>72357</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>134173</t>
+          <t>154907</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>134173</t>
+          <t>154907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134173</t>
+          <t>154907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>125076</t>
+          <t>144058</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125076</t>
+          <t>144058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>125076</t>
+          <t>144058</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>259249</t>
+          <t>298964</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>259249</t>
+          <t>298964</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>259249</t>
+          <t>298964</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
